--- a/test-evidence/M9-Xiong-Ruihan/UT-M9-table.xlsx
+++ b/test-evidence/M9-Xiong-Ruihan/UT-M9-table.xlsx
@@ -31,7 +31,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,11 +41,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002E75B6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -80,15 +75,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -524,7 +516,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>BCrypt-hashed password exists in database</t>
+          <t>DB中存有BCrypt哈希密码</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -534,17 +526,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Returns true</t>
+          <t>返回 true</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Plain text matches hashed password, returns true</t>
+          <t>明文与哈希值匹配返回 true</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Returns true</t>
+          <t>返回 true</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -566,7 +558,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>BCrypt-hashed password exists in database</t>
+          <t>DB中存有BCrypt哈希密码</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -576,17 +568,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Returns false</t>
+          <t>返回 false</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Wrong password does not match hash, returns false</t>
+          <t>错误密码不匹配返回 false</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Returns false</t>
+          <t>返回 false</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -596,40 +588,40 @@
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>UT-M9-S3-01</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>UT-M9-S3-02</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-evidence/M9-Xiong-Ruihan/UT-M9-table.xlsx
+++ b/test-evidence/M9-Xiong-Ruihan/UT-M9-table.xlsx
@@ -31,7 +31,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,12 +80,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -516,7 +524,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>DB中存有BCrypt哈希密码</t>
+          <t>BCrypt-hashed password exists in database</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -526,17 +534,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>返回 true</t>
+          <t>Returns true</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>明文与哈希值匹配返回 true</t>
+          <t>Plain text matches hashed password, returns true</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>返回 true</t>
+          <t>Returns true</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -558,7 +566,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>DB中存有BCrypt哈希密码</t>
+          <t>BCrypt-hashed password exists in database</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -568,17 +576,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>返回 false</t>
+          <t>Returns false</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>错误密码不匹配返回 false</t>
+          <t>Wrong password does not match hash, returns false</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>返回 false</t>
+          <t>Returns false</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -588,40 +596,40 @@
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>UT-M9-S3-01</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>UT-M9-S3-02</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
